--- a/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
@@ -448,13 +448,13 @@
         <v>-141188.275</v>
       </c>
       <c r="E2" t="n">
-        <v>7226.916</v>
+        <v>7567.932</v>
       </c>
       <c r="F2" t="n">
         <v>12997.956</v>
       </c>
       <c r="G2" t="n">
-        <v>172.2754108824</v>
+        <v>171.941319610659</v>
       </c>
       <c r="H2" t="n">
         <v>523.938495245339</v>
@@ -480,13 +480,13 @@
         <v>13047.141</v>
       </c>
       <c r="E3" t="n">
-        <v>16736.016</v>
+        <v>16903.245</v>
       </c>
       <c r="F3" t="n">
         <v>20513.424</v>
       </c>
       <c r="G3" t="n">
-        <v>130.892971118558</v>
+        <v>129.990426041168</v>
       </c>
       <c r="H3" t="n">
         <v>661.765347071613</v>
@@ -512,13 +512,13 @@
         <v>20513.424</v>
       </c>
       <c r="E4" t="n">
-        <v>23378.7235</v>
+        <v>23175.972</v>
       </c>
       <c r="F4" t="n">
         <v>25930.332</v>
       </c>
       <c r="G4" t="n">
-        <v>97.6459031434498</v>
+        <v>97.9475825753949</v>
       </c>
       <c r="H4" t="n">
         <v>689.147645509354</v>
@@ -544,13 +544,13 @@
         <v>25934.704</v>
       </c>
       <c r="E5" t="n">
-        <v>28501.068</v>
+        <v>28566.648</v>
       </c>
       <c r="F5" t="n">
         <v>31478.4</v>
       </c>
       <c r="G5" t="n">
-        <v>74.7382120631881</v>
+        <v>74.0076990585607</v>
       </c>
       <c r="H5" t="n">
         <v>664.308280252339</v>
@@ -576,13 +576,13 @@
         <v>31492.609</v>
       </c>
       <c r="E6" t="n">
-        <v>33904.86</v>
+        <v>33760.584</v>
       </c>
       <c r="F6" t="n">
         <v>35684.264</v>
       </c>
       <c r="G6" t="n">
-        <v>49.98803255146</v>
+        <v>49.7536700175523</v>
       </c>
       <c r="H6" t="n">
         <v>572.419027436461</v>
@@ -608,13 +608,13 @@
         <v>35686.45</v>
       </c>
       <c r="E7" t="n">
-        <v>37788.289</v>
+        <v>37839.66</v>
       </c>
       <c r="F7" t="n">
         <v>39845.315</v>
       </c>
       <c r="G7" t="n">
-        <v>31.0196266156055</v>
+        <v>30.4411999361736</v>
       </c>
       <c r="H7" t="n">
         <v>437.636162284438</v>
@@ -640,13 +640,13 @@
         <v>39846.408</v>
       </c>
       <c r="E8" t="n">
-        <v>42190.893</v>
+        <v>42195.265</v>
       </c>
       <c r="F8" t="n">
         <v>44935.416</v>
       </c>
       <c r="G8" t="n">
-        <v>15.0580421254189</v>
+        <v>14.4447103877453</v>
       </c>
       <c r="H8" t="n">
         <v>359.967765481768</v>
@@ -672,13 +672,13 @@
         <v>44935.416</v>
       </c>
       <c r="E9" t="n">
-        <v>51289.025</v>
+        <v>51368.814</v>
       </c>
       <c r="F9" t="n">
         <v>56924.533</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>73.7982687091112</v>
       </c>
       <c r="H9" t="n">
         <v>709.976242538767</v>
@@ -704,13 +704,13 @@
         <v>56989.02</v>
       </c>
       <c r="E10" t="n">
-        <v>63670.529</v>
+        <v>63573.252</v>
       </c>
       <c r="F10" t="n">
         <v>71579.477</v>
       </c>
       <c r="G10" t="n">
-        <v>48.2328067655976</v>
+        <v>48.7115047071964</v>
       </c>
       <c r="H10" t="n">
         <v>548.667657140245</v>
@@ -736,13 +736,13 @@
         <v>71579.477</v>
       </c>
       <c r="E11" t="n">
-        <v>79686.258</v>
+        <v>79758.396</v>
       </c>
       <c r="F11" t="n">
         <v>87667.344</v>
       </c>
       <c r="G11" t="n">
-        <v>18.2294159885113</v>
+        <v>18.0648635710867</v>
       </c>
       <c r="H11" t="n">
         <v>243.476503416874</v>
@@ -820,7 +820,7 @@
         <v>-141188.275</v>
       </c>
       <c r="G2" t="n">
-        <v>17103.264</v>
+        <v>17221.308</v>
       </c>
       <c r="H2" t="n">
         <v>26861.568</v>
@@ -855,7 +855,7 @@
         <v>26909.66</v>
       </c>
       <c r="G3" t="n">
-        <v>34298.34</v>
+        <v>34272.108</v>
       </c>
       <c r="H3" t="n">
         <v>41081.498</v>
@@ -890,7 +890,7 @@
         <v>41082.591</v>
       </c>
       <c r="G4" t="n">
-        <v>48034.071</v>
+        <v>48096.372</v>
       </c>
       <c r="H4" t="n">
         <v>54851.112</v>
@@ -925,7 +925,7 @@
         <v>54851.112</v>
       </c>
       <c r="G5" t="n">
-        <v>62868.8135</v>
+        <v>62816.896</v>
       </c>
       <c r="H5" t="n">
         <v>71246.112</v>
@@ -960,7 +960,7 @@
         <v>71246.112</v>
       </c>
       <c r="G6" t="n">
-        <v>80459.009</v>
+        <v>80283.036</v>
       </c>
       <c r="H6" t="n">
         <v>91182.432</v>
@@ -995,7 +995,7 @@
         <v>91182.432</v>
       </c>
       <c r="G7" t="n">
-        <v>103879.2665</v>
+        <v>103755.211</v>
       </c>
       <c r="H7" t="n">
         <v>117177.251</v>
@@ -1030,7 +1030,7 @@
         <v>117270.156</v>
       </c>
       <c r="G8" t="n">
-        <v>132530.622</v>
+        <v>133385.348</v>
       </c>
       <c r="H8" t="n">
         <v>149707.117</v>
@@ -1100,7 +1100,7 @@
         <v>194759.484</v>
       </c>
       <c r="G10" t="n">
-        <v>230279.798</v>
+        <v>231015.387</v>
       </c>
       <c r="H10" t="n">
         <v>286474.207</v>
@@ -1135,7 +1135,7 @@
         <v>286474.207</v>
       </c>
       <c r="G11" t="n">
-        <v>441156.66</v>
+        <v>438279.884</v>
       </c>
       <c r="H11" t="n">
         <v>2550288.156</v>
@@ -1231,7 +1231,7 @@
         <v>26.232</v>
       </c>
       <c r="H2" t="n">
-        <v>11209.808</v>
+        <v>10964.976</v>
       </c>
       <c r="I2" t="n">
         <v>18517.606</v>
@@ -1246,10 +1246,10 @@
         <v>0.152370804137726</v>
       </c>
       <c r="M2" t="n">
-        <v>165.906068826126</v>
+        <v>166.650710068613</v>
       </c>
       <c r="N2" t="n">
-        <v>5.37699401550012</v>
+        <v>5.47249213544252</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         <v>18808.344</v>
       </c>
       <c r="H3" t="n">
-        <v>23813.7375</v>
+        <v>23124.601</v>
       </c>
       <c r="I3" t="n">
         <v>28710.924</v>
@@ -1293,10 +1293,10 @@
         <v>0.20763862267393</v>
       </c>
       <c r="M3" t="n">
-        <v>127.572004148716</v>
+        <v>129.667969788841</v>
       </c>
       <c r="N3" t="n">
-        <v>3.29167583792611</v>
+        <v>3.3349785184263</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>28828.968</v>
       </c>
       <c r="H4" t="n">
-        <v>34114.716</v>
+        <v>33904.86</v>
       </c>
       <c r="I4" t="n">
         <v>38364.3</v>
@@ -1340,10 +1340,10 @@
         <v>0.216455980423571</v>
       </c>
       <c r="M4" t="n">
-        <v>96.242221158449</v>
+        <v>96.8804850805808</v>
       </c>
       <c r="N4" t="n">
-        <v>3.04573842466749</v>
+        <v>3.04440018681961</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>38602.574</v>
       </c>
       <c r="H5" t="n">
-        <v>42436.818</v>
+        <v>42692.58</v>
       </c>
       <c r="I5" t="n">
         <v>46037.16</v>
@@ -1387,10 +1387,10 @@
         <v>0.19956829788813</v>
       </c>
       <c r="M5" t="n">
-        <v>70.9310674964098</v>
+        <v>70.1531833413116</v>
       </c>
       <c r="N5" t="n">
-        <v>3.32216112485395</v>
+        <v>3.33887543020809</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>46151.925</v>
       </c>
       <c r="H6" t="n">
-        <v>50504.251</v>
+        <v>50839.802</v>
       </c>
       <c r="I6" t="n">
         <v>54929.808</v>
@@ -1434,10 +1434,10 @@
         <v>0.14969748408733</v>
       </c>
       <c r="M6" t="n">
-        <v>46.3944736982075</v>
+        <v>45.3739162810489</v>
       </c>
       <c r="N6" t="n">
-        <v>4.26781723438041</v>
+        <v>4.3350078087061</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>55060.968</v>
       </c>
       <c r="H7" t="n">
-        <v>60028.653</v>
+        <v>59778.356</v>
       </c>
       <c r="I7" t="n">
         <v>65580</v>
@@ -1481,10 +1481,10 @@
         <v>0.0742451231161157</v>
       </c>
       <c r="M7" t="n">
-        <v>17.4265996489549</v>
+        <v>18.1878623477475</v>
       </c>
       <c r="N7" t="n">
-        <v>9.55935847191215</v>
+        <v>9.19759694864239</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>65684.928</v>
       </c>
       <c r="H8" t="n">
-        <v>71626.476</v>
+        <v>70313.783</v>
       </c>
       <c r="I8" t="n">
         <v>78515.655</v>
@@ -1556,7 +1556,7 @@
         <v>78696</v>
       </c>
       <c r="H9" t="n">
-        <v>88323.144</v>
+        <v>86919.732</v>
       </c>
       <c r="I9" t="n">
         <v>103904.952</v>
@@ -1599,7 +1599,7 @@
         <v>104062.344</v>
       </c>
       <c r="H10" t="n">
-        <v>117369.619</v>
+        <v>115971.672</v>
       </c>
       <c r="I10" t="n">
         <v>140946.722</v>
@@ -1642,7 +1642,7 @@
         <v>141390.48</v>
       </c>
       <c r="H11" t="n">
-        <v>193446.791</v>
+        <v>202655.316</v>
       </c>
       <c r="I11" t="n">
         <v>1410940.584</v>
@@ -1685,7 +1685,7 @@
         <v>-141188.275</v>
       </c>
       <c r="H12" t="n">
-        <v>41493.559</v>
+        <v>41866.272</v>
       </c>
       <c r="I12" t="n">
         <v>56989.02</v>
@@ -1700,10 +1700,10 @@
         <v>0.614875562709463</v>
       </c>
       <c r="M12" t="n">
-        <v>105.349948141056</v>
+        <v>104.499760651029</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28762580552962</v>
+        <v>2.28570623827767</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>57015.252</v>
       </c>
       <c r="H13" t="n">
-        <v>71579.477</v>
+        <v>71724.846</v>
       </c>
       <c r="I13" t="n">
         <v>84716.244</v>
@@ -1747,10 +1747,10 @@
         <v>0.379612314019876</v>
       </c>
       <c r="M13" t="n">
-        <v>36.7216172012127</v>
+        <v>36.3900191479177</v>
       </c>
       <c r="N13" t="n">
-        <v>3.80443072194467</v>
+        <v>3.83131704243525</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>84720.616</v>
       </c>
       <c r="H14" t="n">
-        <v>95569.734</v>
+        <v>95576.292</v>
       </c>
       <c r="I14" t="n">
         <v>107827.729</v>
@@ -1822,7 +1822,7 @@
         <v>107827.729</v>
       </c>
       <c r="H15" t="n">
-        <v>120230</v>
+        <v>120264.976</v>
       </c>
       <c r="I15" t="n">
         <v>131737.104</v>
@@ -1865,7 +1865,7 @@
         <v>131750.22</v>
       </c>
       <c r="H16" t="n">
-        <v>142222.253</v>
+        <v>142417.9</v>
       </c>
       <c r="I16" t="n">
         <v>154780.823</v>
@@ -1908,7 +1908,7 @@
         <v>154780.823</v>
       </c>
       <c r="H17" t="n">
-        <v>168053.122</v>
+        <v>168234.56</v>
       </c>
       <c r="I17" t="n">
         <v>181274.05</v>
@@ -1951,7 +1951,7 @@
         <v>181274.05</v>
       </c>
       <c r="H18" t="n">
-        <v>197798.024</v>
+        <v>198228.666</v>
       </c>
       <c r="I18" t="n">
         <v>218698.37</v>
@@ -1994,7 +1994,7 @@
         <v>218761.764</v>
       </c>
       <c r="H19" t="n">
-        <v>241545.8955</v>
+        <v>241966.154</v>
       </c>
       <c r="I19" t="n">
         <v>273817.267</v>
@@ -2080,7 +2080,7 @@
         <v>414943.241</v>
       </c>
       <c r="H21" t="n">
-        <v>575744.308</v>
+        <v>575185.785</v>
       </c>
       <c r="I21" t="n">
         <v>2550288.156</v>
@@ -2123,7 +2123,7 @@
         <v>21.86</v>
       </c>
       <c r="H22" t="n">
-        <v>12015.8955</v>
+        <v>12197.88</v>
       </c>
       <c r="I22" t="n">
         <v>19282.706</v>
@@ -2138,10 +2138,10 @@
         <v>0.321453626335432</v>
       </c>
       <c r="M22" t="n">
-        <v>145.181606031594</v>
+        <v>144.351364289134</v>
       </c>
       <c r="N22" t="n">
-        <v>5.73234421476292</v>
+        <v>5.67929922082402</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>19290.357</v>
       </c>
       <c r="H23" t="n">
-        <v>24922.0395</v>
+        <v>24618.732</v>
       </c>
       <c r="I23" t="n">
         <v>29524.116</v>
@@ -2185,10 +2185,10 @@
         <v>0.355528782896852</v>
       </c>
       <c r="M23" t="n">
-        <v>86.3017592149354</v>
+        <v>87.6854954523696</v>
       </c>
       <c r="N23" t="n">
-        <v>4.64939850166933</v>
+        <v>4.63240539948099</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         <v>29589.696</v>
       </c>
       <c r="H24" t="n">
-        <v>34081.3795</v>
+        <v>34101.6</v>
       </c>
       <c r="I24" t="n">
         <v>37747.848</v>
@@ -2232,10 +2232,10 @@
         <v>0.251497372804517</v>
       </c>
       <c r="M24" t="n">
-        <v>44.515418062869</v>
+        <v>44.4231689803734</v>
       </c>
       <c r="N24" t="n">
-        <v>6.59131972391826</v>
+        <v>6.60109081745987</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>37760.964</v>
       </c>
       <c r="H25" t="n">
-        <v>41586.464</v>
+        <v>41339.446</v>
       </c>
       <c r="I25" t="n">
         <v>45840.42</v>
@@ -2279,10 +2279,10 @@
         <v>0.0715202179631991</v>
       </c>
       <c r="M25" t="n">
-        <v>10.276049146322</v>
+        <v>11.402983883836</v>
       </c>
       <c r="N25" t="n">
-        <v>23.4003219403971</v>
+        <v>21.2137202410713</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>45866.652</v>
       </c>
       <c r="H26" t="n">
-        <v>50048.47</v>
+        <v>50155.584</v>
       </c>
       <c r="I26" t="n">
         <v>54798.648</v>
@@ -2354,7 +2354,7 @@
         <v>54798.648</v>
       </c>
       <c r="H27" t="n">
-        <v>60140.139</v>
+        <v>60281.136</v>
       </c>
       <c r="I27" t="n">
         <v>66183.336</v>
@@ -2397,7 +2397,7 @@
         <v>66183.336</v>
       </c>
       <c r="H28" t="n">
-        <v>72179.534</v>
+        <v>72357.693</v>
       </c>
       <c r="I28" t="n">
         <v>79958.415</v>
@@ -2440,7 +2440,7 @@
         <v>79959.508</v>
       </c>
       <c r="H29" t="n">
-        <v>88800.2385</v>
+        <v>89337.448</v>
       </c>
       <c r="I29" t="n">
         <v>101163.708</v>
@@ -2483,7 +2483,7 @@
         <v>101399.796</v>
       </c>
       <c r="H30" t="n">
-        <v>117009.4755</v>
+        <v>117429.734</v>
       </c>
       <c r="I30" t="n">
         <v>142479.108</v>
@@ -2526,7 +2526,7 @@
         <v>142479.108</v>
       </c>
       <c r="H31" t="n">
-        <v>191845.546</v>
+        <v>190485.854</v>
       </c>
       <c r="I31" t="n">
         <v>1732558.02</v>

--- a/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
@@ -439,31 +439,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="C2" t="n">
-        <v>4.59079187784168</v>
+        <v>4.43433371412791</v>
       </c>
       <c r="D2" t="n">
         <v>-141188.275</v>
       </c>
       <c r="E2" t="n">
-        <v>7567.932</v>
+        <v>7301.24</v>
       </c>
       <c r="F2" t="n">
-        <v>12997.956</v>
+        <v>12553.105</v>
       </c>
       <c r="G2" t="n">
-        <v>171.941319610659</v>
+        <v>172.060708135807</v>
       </c>
       <c r="H2" t="n">
-        <v>523.938495245339</v>
+        <v>518.233667043824</v>
       </c>
       <c r="I2" t="n">
-        <v>2405.29258846089</v>
+        <v>2298.02102156857</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0965107835682653</v>
+        <v>0.0962900211632315</v>
       </c>
     </row>
     <row r="3">
@@ -471,31 +471,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C3" t="n">
-        <v>4.62043692390843</v>
+        <v>4.45622329904797</v>
       </c>
       <c r="D3" t="n">
-        <v>13047.141</v>
+        <v>12568.407</v>
       </c>
       <c r="E3" t="n">
-        <v>16903.245</v>
+        <v>16434.348</v>
       </c>
       <c r="F3" t="n">
-        <v>20513.424</v>
+        <v>19962.552</v>
       </c>
       <c r="G3" t="n">
-        <v>129.990426041168</v>
+        <v>129.324441794024</v>
       </c>
       <c r="H3" t="n">
-        <v>661.765347071613</v>
+        <v>653.195073778606</v>
       </c>
       <c r="I3" t="n">
-        <v>3057.64504457276</v>
+        <v>2910.78310659558</v>
       </c>
       <c r="J3" t="n">
-        <v>0.122685996930696</v>
+        <v>0.121965536566047</v>
       </c>
     </row>
     <row r="4">
@@ -503,31 +503,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="C4" t="n">
-        <v>4.60699258564647</v>
+        <v>4.44154325612709</v>
       </c>
       <c r="D4" t="n">
-        <v>20513.424</v>
+        <v>19964.738</v>
       </c>
       <c r="E4" t="n">
-        <v>23175.972</v>
+        <v>22795.608</v>
       </c>
       <c r="F4" t="n">
-        <v>25930.332</v>
+        <v>25536.852</v>
       </c>
       <c r="G4" t="n">
-        <v>97.9475825753949</v>
+        <v>98.1724704345243</v>
       </c>
       <c r="H4" t="n">
-        <v>689.147645509354</v>
+        <v>675.386583059987</v>
       </c>
       <c r="I4" t="n">
-        <v>3174.89809327731</v>
+        <v>2999.7587232688</v>
       </c>
       <c r="J4" t="n">
-        <v>0.127390698412975</v>
+        <v>0.125693728750568</v>
       </c>
     </row>
     <row r="5">
@@ -535,31 +535,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="C5" t="n">
-        <v>4.60352052337934</v>
+        <v>4.45229041082673</v>
       </c>
       <c r="D5" t="n">
-        <v>25934.704</v>
+        <v>25539.038</v>
       </c>
       <c r="E5" t="n">
-        <v>28566.648</v>
+        <v>27974.242</v>
       </c>
       <c r="F5" t="n">
-        <v>31478.4</v>
+        <v>30655.371</v>
       </c>
       <c r="G5" t="n">
-        <v>74.0076990585607</v>
+        <v>73.4797649732394</v>
       </c>
       <c r="H5" t="n">
-        <v>664.308280252339</v>
+        <v>667.016637222493</v>
       </c>
       <c r="I5" t="n">
-        <v>3058.15680199248</v>
+        <v>2969.7517777676</v>
       </c>
       <c r="J5" t="n">
-        <v>0.122706530860669</v>
+        <v>0.124436399339637</v>
       </c>
     </row>
     <row r="6">
@@ -567,31 +567,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58360715656805</v>
+        <v>4.45096689800677</v>
       </c>
       <c r="D6" t="n">
-        <v>31492.609</v>
+        <v>30689.254</v>
       </c>
       <c r="E6" t="n">
-        <v>33760.584</v>
+        <v>32999.856</v>
       </c>
       <c r="F6" t="n">
-        <v>35684.264</v>
+        <v>34783.632</v>
       </c>
       <c r="G6" t="n">
-        <v>49.7536700175523</v>
+        <v>48.8226617649368</v>
       </c>
       <c r="H6" t="n">
-        <v>572.419027436461</v>
+        <v>558.27367972807</v>
       </c>
       <c r="I6" t="n">
-        <v>2623.74395071348</v>
+        <v>2484.85766849807</v>
       </c>
       <c r="J6" t="n">
-        <v>0.105276000841081</v>
+        <v>0.104118715730451</v>
       </c>
     </row>
     <row r="7">
@@ -599,31 +599,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C7" t="n">
-        <v>4.62155617251596</v>
+        <v>4.44582902388394</v>
       </c>
       <c r="D7" t="n">
-        <v>35686.45</v>
+        <v>34784.725</v>
       </c>
       <c r="E7" t="n">
-        <v>37839.66</v>
+        <v>37039.584</v>
       </c>
       <c r="F7" t="n">
-        <v>39845.315</v>
+        <v>38940.311</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4411999361736</v>
+        <v>30.268801925026</v>
       </c>
       <c r="H7" t="n">
-        <v>437.636162284438</v>
+        <v>434.886008821099</v>
       </c>
       <c r="I7" t="n">
-        <v>2022.56010712184</v>
+        <v>1933.42884009789</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0811538944113024</v>
+        <v>0.081013142257312</v>
       </c>
     </row>
     <row r="8">
@@ -631,31 +631,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="C8" t="n">
-        <v>4.61181081079348</v>
+        <v>4.44939062397037</v>
       </c>
       <c r="D8" t="n">
-        <v>39846.408</v>
+        <v>38965.45</v>
       </c>
       <c r="E8" t="n">
-        <v>42195.265</v>
+        <v>41039.964</v>
       </c>
       <c r="F8" t="n">
-        <v>44935.416</v>
+        <v>43886.136</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4447103877453</v>
+        <v>14.8072520584336</v>
       </c>
       <c r="H8" t="n">
-        <v>359.967765481768</v>
+        <v>354.772265564442</v>
       </c>
       <c r="I8" t="n">
-        <v>1660.10323238599</v>
+        <v>1578.52039204715</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0666105506375432</v>
+        <v>0.0661420241722004</v>
       </c>
     </row>
     <row r="9">
@@ -663,31 +663,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="C9" t="n">
-        <v>4.60536199146873</v>
+        <v>4.4436894162443</v>
       </c>
       <c r="D9" t="n">
-        <v>44935.416</v>
+        <v>43912.368</v>
       </c>
       <c r="E9" t="n">
-        <v>51368.814</v>
+        <v>50666.015</v>
       </c>
       <c r="F9" t="n">
-        <v>56924.533</v>
+        <v>55842.463</v>
       </c>
       <c r="G9" t="n">
-        <v>73.7982687091112</v>
+        <v>73.02202172061</v>
       </c>
       <c r="H9" t="n">
-        <v>709.976242538767</v>
+        <v>693.41626230478</v>
       </c>
       <c r="I9" t="n">
-        <v>3269.69760223382</v>
+        <v>3081.32650585543</v>
       </c>
       <c r="J9" t="n">
-        <v>0.131194466376661</v>
+        <v>0.129111523208402</v>
       </c>
     </row>
     <row r="10">
@@ -695,31 +695,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="C10" t="n">
-        <v>4.60344111454769</v>
+        <v>4.44806443106848</v>
       </c>
       <c r="D10" t="n">
-        <v>56989.02</v>
+        <v>55847.928</v>
       </c>
       <c r="E10" t="n">
-        <v>63573.252</v>
+        <v>61893.311</v>
       </c>
       <c r="F10" t="n">
-        <v>71579.477</v>
+        <v>69351.943</v>
       </c>
       <c r="G10" t="n">
-        <v>48.7115047071964</v>
+        <v>49.5550509691438</v>
       </c>
       <c r="H10" t="n">
-        <v>548.667657140245</v>
+        <v>553.028149161065</v>
       </c>
       <c r="I10" t="n">
-        <v>2525.75925110196</v>
+        <v>2459.90483966297</v>
       </c>
       <c r="J10" t="n">
-        <v>0.101344429196709</v>
+        <v>0.103073160274663</v>
       </c>
     </row>
     <row r="11">
@@ -727,31 +727,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C11" t="n">
-        <v>4.61921416123918</v>
+        <v>4.45014132869324</v>
       </c>
       <c r="D11" t="n">
-        <v>71579.477</v>
+        <v>69357.408</v>
       </c>
       <c r="E11" t="n">
-        <v>79758.396</v>
+        <v>77789.903</v>
       </c>
       <c r="F11" t="n">
-        <v>87667.344</v>
+        <v>85948.055</v>
       </c>
       <c r="G11" t="n">
-        <v>18.0648635710867</v>
+        <v>19.0108609284134</v>
       </c>
       <c r="H11" t="n">
-        <v>243.476503416874</v>
+        <v>258.253995518046</v>
       </c>
       <c r="I11" t="n">
-        <v>1124.67011251223</v>
+        <v>1149.26677875501</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0451266487640984</v>
+        <v>0.0481557485374889</v>
       </c>
     </row>
   </sheetData>
@@ -826,13 +826,13 @@
         <v>26861.568</v>
       </c>
       <c r="I2" t="n">
-        <v>630.368176655975</v>
+        <v>623.655609783921</v>
       </c>
       <c r="J2" t="n">
-        <v>9158.14934058373</v>
+        <v>9060.62746027714</v>
       </c>
       <c r="K2" t="n">
-        <v>0.367464720564618</v>
+        <v>0.379651883822513</v>
       </c>
     </row>
     <row r="3">
@@ -861,13 +861,13 @@
         <v>41081.498</v>
       </c>
       <c r="I3" t="n">
-        <v>528.598205035093</v>
+        <v>501.997435171046</v>
       </c>
       <c r="J3" t="n">
-        <v>7682.92491509676</v>
+        <v>7296.29530568355</v>
       </c>
       <c r="K3" t="n">
-        <v>0.308272310491174</v>
+        <v>0.305724109050102</v>
       </c>
     </row>
     <row r="4">
@@ -881,10 +881,10 @@
         <v>14.5338139186254</v>
       </c>
       <c r="D4" t="n">
-        <v>6.82600388755977</v>
+        <v>6.06203075849541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.469663635834232</v>
+        <v>0.417098415628316</v>
       </c>
       <c r="F4" t="n">
         <v>41082.591</v>
@@ -896,13 +896,13 @@
         <v>54851.112</v>
       </c>
       <c r="I4" t="n">
-        <v>260.781149336131</v>
+        <v>249.191875277674</v>
       </c>
       <c r="J4" t="n">
-        <v>3790.14469793659</v>
+        <v>3621.70834531902</v>
       </c>
       <c r="K4" t="n">
-        <v>0.152077063883953</v>
+        <v>0.151754213710275</v>
       </c>
     </row>
     <row r="5">
@@ -916,10 +916,10 @@
         <v>14.5342531613302</v>
       </c>
       <c r="D5" t="n">
-        <v>5.39198623751163</v>
+        <v>5.23161965573144</v>
       </c>
       <c r="E5" t="n">
-        <v>0.370984747386783</v>
+        <v>0.359951047890831</v>
       </c>
       <c r="F5" t="n">
         <v>54851.112</v>
@@ -931,13 +931,13 @@
         <v>71246.112</v>
       </c>
       <c r="I5" t="n">
-        <v>212.401955621922</v>
+        <v>200.187189067182</v>
       </c>
       <c r="J5" t="n">
-        <v>3087.10379497064</v>
+        <v>2909.57128555749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.123868009920501</v>
+        <v>0.121914759714004</v>
       </c>
     </row>
     <row r="6">
@@ -951,10 +951,10 @@
         <v>14.5372594700653</v>
       </c>
       <c r="D6" t="n">
-        <v>4.78596156684474</v>
+        <v>4.11604036177709</v>
       </c>
       <c r="E6" t="n">
-        <v>0.329220344226493</v>
+        <v>0.283137297662789</v>
       </c>
       <c r="F6" t="n">
         <v>71246.112</v>
@@ -966,13 +966,13 @@
         <v>91182.432</v>
       </c>
       <c r="I6" t="n">
-        <v>82.8356980395582</v>
+        <v>67.23531758462</v>
       </c>
       <c r="J6" t="n">
-        <v>1204.20403578504</v>
+        <v>977.417257279866</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0483178951397542</v>
+        <v>0.0409550337031057</v>
       </c>
     </row>
     <row r="7">
@@ -1237,19 +1237,19 @@
         <v>18517.606</v>
       </c>
       <c r="J2" t="n">
-        <v>641.542606414887</v>
+        <v>639.485131863176</v>
       </c>
       <c r="K2" t="n">
-        <v>777.295529530808</v>
+        <v>774.802685321901</v>
       </c>
       <c r="L2" t="n">
-        <v>0.152370804137726</v>
+        <v>0.157994349106492</v>
       </c>
       <c r="M2" t="n">
-        <v>166.650710068613</v>
+        <v>165.984590293497</v>
       </c>
       <c r="N2" t="n">
-        <v>5.47249213544252</v>
+        <v>5.49445402494167</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -1284,19 +1284,19 @@
         <v>28710.924</v>
       </c>
       <c r="J3" t="n">
-        <v>854.926974647644</v>
+        <v>846.206308143556</v>
       </c>
       <c r="K3" t="n">
-        <v>1059.23555418461</v>
+        <v>1048.43084186269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.20763862267393</v>
+        <v>0.213791396934109</v>
       </c>
       <c r="M3" t="n">
-        <v>129.667969788841</v>
+        <v>128.263155586076</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3349785184263</v>
+        <v>3.37150518243355</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -1331,19 +1331,19 @@
         <v>38364.3</v>
       </c>
       <c r="J4" t="n">
-        <v>899.917374475178</v>
+        <v>882.273781106785</v>
       </c>
       <c r="K4" t="n">
-        <v>1104.21590852385</v>
+        <v>1082.56688047584</v>
       </c>
       <c r="L4" t="n">
-        <v>0.216455980423571</v>
+        <v>0.220752267493712</v>
       </c>
       <c r="M4" t="n">
-        <v>96.8804850805808</v>
+        <v>94.8207726180492</v>
       </c>
       <c r="N4" t="n">
-        <v>3.04440018681961</v>
+        <v>3.11053114982056</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -1378,19 +1378,19 @@
         <v>46037.16</v>
       </c>
       <c r="J5" t="n">
-        <v>826.946099105548</v>
+        <v>797.123131909767</v>
       </c>
       <c r="K5" t="n">
-        <v>1018.06607021842</v>
+        <v>981.350556295445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.19956829788813</v>
+        <v>0.200112680717899</v>
       </c>
       <c r="M5" t="n">
-        <v>70.1531833413116</v>
+        <v>67.5596189058994</v>
       </c>
       <c r="N5" t="n">
-        <v>3.33887543020809</v>
+        <v>3.46705241981072</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>54929.808</v>
       </c>
       <c r="J6" t="n">
-        <v>647.160006089242</v>
+        <v>602.694731190546</v>
       </c>
       <c r="K6" t="n">
-        <v>763.658010611504</v>
+        <v>711.188353879117</v>
       </c>
       <c r="L6" t="n">
-        <v>0.14969748408733</v>
+        <v>0.145022394981202</v>
       </c>
       <c r="M6" t="n">
-        <v>45.3739162810489</v>
+        <v>42.2854099792372</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3350078087061</v>
+        <v>4.65163472428207</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>1.27877796566927</v>
       </c>
       <c r="E7" t="n">
-        <v>1.27877796566927</v>
+        <v>1.14895850830196</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.898481627888106</v>
       </c>
       <c r="G7" t="n">
         <v>55060.968</v>
@@ -1472,19 +1472,19 @@
         <v>65580</v>
       </c>
       <c r="J7" t="n">
-        <v>296.181001782542</v>
+        <v>239.017676531937</v>
       </c>
       <c r="K7" t="n">
-        <v>378.749738929364</v>
+        <v>305.650538154505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0742451231161157</v>
+        <v>0.0623269107665869</v>
       </c>
       <c r="M7" t="n">
-        <v>18.1878623477475</v>
+        <v>14.5563409421775</v>
       </c>
       <c r="N7" t="n">
-        <v>9.19759694864239</v>
+        <v>11.492216889978</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1504,10 +1504,10 @@
         <v>1.22912405460904</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0305471244128958</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0248527594089046</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>65684.928</v>
@@ -1519,13 +1519,13 @@
         <v>78515.655</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0983130331240317</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.120838913894323</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0000236876731972477</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1691,19 +1691,19 @@
         <v>56989.02</v>
       </c>
       <c r="J12" t="n">
-        <v>750.912629981052</v>
+        <v>745.658178018356</v>
       </c>
       <c r="K12" t="n">
-        <v>5327.04527319697</v>
+        <v>5289.76969362412</v>
       </c>
       <c r="L12" t="n">
-        <v>0.614875562709463</v>
+        <v>0.637035867065899</v>
       </c>
       <c r="M12" t="n">
-        <v>104.499760651029</v>
+        <v>102.592235840468</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28570623827767</v>
+        <v>2.32820498414718</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -1738,19 +1738,19 @@
         <v>84716.244</v>
       </c>
       <c r="J13" t="n">
-        <v>463.730064415223</v>
+        <v>424.181890552559</v>
       </c>
       <c r="K13" t="n">
-        <v>3288.81501508374</v>
+        <v>3008.33583549315</v>
       </c>
       <c r="L13" t="n">
-        <v>0.379612314019876</v>
+        <v>0.362287573634576</v>
       </c>
       <c r="M13" t="n">
-        <v>36.3900191479177</v>
+        <v>33.1220681997491</v>
       </c>
       <c r="N13" t="n">
-        <v>3.83131704243525</v>
+        <v>4.2093295531895</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1770,10 +1770,10 @@
         <v>7.09595053984403</v>
       </c>
       <c r="E14" t="n">
-        <v>1.04216138948432</v>
+        <v>0.372240184416668</v>
       </c>
       <c r="F14" t="n">
-        <v>0.146867059406988</v>
+        <v>0.0524581142901892</v>
       </c>
       <c r="G14" t="n">
         <v>84720.616</v>
@@ -1785,13 +1785,13 @@
         <v>107827.729</v>
       </c>
       <c r="J14" t="n">
-        <v>6.72988272702142</v>
+        <v>0.79171371285735</v>
       </c>
       <c r="K14" t="n">
-        <v>47.7549149698946</v>
+        <v>5.61796134815203</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00551212327066152</v>
+        <v>0.000676559299524212</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2129,19 +2129,19 @@
         <v>19282.706</v>
       </c>
       <c r="J22" t="n">
-        <v>578.485115415805</v>
+        <v>574.75040123231</v>
       </c>
       <c r="K22" t="n">
-        <v>3586.64131515708</v>
+        <v>3563.48587029969</v>
       </c>
       <c r="L22" t="n">
-        <v>0.321453626335432</v>
+        <v>0.334351397679096</v>
       </c>
       <c r="M22" t="n">
-        <v>144.351364289134</v>
+        <v>143.239836673957</v>
       </c>
       <c r="N22" t="n">
-        <v>5.67929922082402</v>
+        <v>5.7233700468273</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -2176,19 +2176,19 @@
         <v>29524.116</v>
       </c>
       <c r="J23" t="n">
-        <v>638.853567253709</v>
+        <v>623.223526179425</v>
       </c>
       <c r="K23" t="n">
-        <v>3966.83725737397</v>
+        <v>3869.78555030706</v>
       </c>
       <c r="L23" t="n">
-        <v>0.355528782896852</v>
+        <v>0.363090595713438</v>
       </c>
       <c r="M23" t="n">
-        <v>87.6854954523696</v>
+        <v>85.4421219752872</v>
       </c>
       <c r="N23" t="n">
-        <v>4.63240539948099</v>
+        <v>4.75403411337569</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -2223,19 +2223,19 @@
         <v>37747.848</v>
       </c>
       <c r="J24" t="n">
-        <v>451.100957883838</v>
+        <v>420.772466959569</v>
       </c>
       <c r="K24" t="n">
-        <v>2806.09952433041</v>
+        <v>2617.43939743668</v>
       </c>
       <c r="L24" t="n">
-        <v>0.251497372804517</v>
+        <v>0.245586639803256</v>
       </c>
       <c r="M24" t="n">
-        <v>44.4231689803734</v>
+        <v>41.315672421815</v>
       </c>
       <c r="N24" t="n">
-        <v>6.60109081745987</v>
+        <v>7.09758199854391</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -2255,10 +2255,10 @@
         <v>6.20768140841987</v>
       </c>
       <c r="E25" t="n">
-        <v>4.81041065961307</v>
+        <v>4.04643753054872</v>
       </c>
       <c r="F25" t="n">
-        <v>0.774912619241124</v>
+        <v>0.651843621526756</v>
       </c>
       <c r="G25" t="n">
         <v>37760.964</v>
@@ -2270,19 +2270,19 @@
         <v>45840.42</v>
       </c>
       <c r="J25" t="n">
-        <v>128.54909600642</v>
+        <v>97.8135715526791</v>
       </c>
       <c r="K25" t="n">
-        <v>797.991833348233</v>
+        <v>607.195489618713</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0715202179631991</v>
+        <v>0.056971366804209</v>
       </c>
       <c r="M25" t="n">
-        <v>11.402983883836</v>
+        <v>7.63594110057332</v>
       </c>
       <c r="N25" t="n">
-        <v>21.2137202410713</v>
+        <v>31.6790958493616</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>

--- a/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">magi_decile_int</t>
   </si>
@@ -43,7 +43,19 @@
     <t xml:space="preserve">total_match_dollars_M_full_num</t>
   </si>
   <si>
+    <t xml:space="preserve">total_seed_dollars_M_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_federal_dollars_M_full_num</t>
+  </si>
+  <si>
     <t xml:space="preserve">share_of_full_dollars_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share_of_seed_dollars_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share_of_federal_dollars_incl_seed_num</t>
   </si>
   <si>
     <t xml:space="preserve">weighted_n_eligible_M_num</t>
@@ -56,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">share_of_filing_group_dollars_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share_of_filing_group_seed_num</t>
   </si>
   <si>
     <t xml:space="preserve">match_rate_at_median_pp_num</t>
@@ -433,6 +448,18 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -463,7 +490,19 @@
         <v>2298.02102156857</v>
       </c>
       <c r="J2" t="n">
+        <v>443.433371412791</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2741.45439298136</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.0962900211632315</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0997096287799104</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0968271564732164</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +534,19 @@
         <v>2910.78310659558</v>
       </c>
       <c r="J3" t="n">
+        <v>445.622329904797</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3356.40543650038</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.121965536566047</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.100201834041678</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.118547000168821</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +578,19 @@
         <v>2999.7587232688</v>
       </c>
       <c r="J4" t="n">
+        <v>444.154325612709</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3443.91304888151</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.125693728750568</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0998717412420648</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.121637736713014</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +622,19 @@
         <v>2969.7517777676</v>
       </c>
       <c r="J5" t="n">
+        <v>445.229041082673</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3414.98081885027</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.124436399339637</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.100113399825885</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.120615861035809</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +666,19 @@
         <v>2484.85766849807</v>
       </c>
       <c r="J6" t="n">
+        <v>445.096689800677</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2929.95435829875</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.104118715730451</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.100083639555127</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.103484905616777</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +710,19 @@
         <v>1933.42884009789</v>
       </c>
       <c r="J7" t="n">
+        <v>444.582902388394</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2378.01174248628</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.081013142257312</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0999681102435026</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0839904963126013</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +754,19 @@
         <v>1578.52039204715</v>
       </c>
       <c r="J8" t="n">
+        <v>444.939062397037</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2023.45945444419</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.0661420241722004</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.100048195741206</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0714678404697462</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +798,19 @@
         <v>3081.32650585543</v>
       </c>
       <c r="J9" t="n">
+        <v>444.36894162443</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3525.69544747986</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.129111523208402</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0999199994116985</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.12452626082128</v>
       </c>
     </row>
     <row r="10">
@@ -719,7 +842,19 @@
         <v>2459.90483966297</v>
       </c>
       <c r="J10" t="n">
+        <v>444.806443106848</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2904.71128276982</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.103073160274663</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.100018375206609</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.102593329513829</v>
       </c>
     </row>
     <row r="11">
@@ -751,7 +886,19 @@
         <v>1149.26677875501</v>
       </c>
       <c r="J11" t="n">
+        <v>445.014132869324</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1594.28091162434</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.0481557485374889</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.100065075952319</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0563094128749059</v>
       </c>
     </row>
   </sheetData>
@@ -776,10 +923,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -798,6 +945,18 @@
       </c>
       <c r="K1" t="s">
         <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -832,7 +991,19 @@
         <v>9060.62746027714</v>
       </c>
       <c r="K2" t="n">
+        <v>1452.82545657152</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10513.4529168487</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.379651883822513</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.326679714012547</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.371331273378007</v>
       </c>
     </row>
     <row r="3">
@@ -867,7 +1038,19 @@
         <v>7296.29530568355</v>
       </c>
       <c r="K3" t="n">
+        <v>1453.45270602777</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8749.74801171132</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.305724109050102</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.326820756194906</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.309037867637052</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +1085,19 @@
         <v>3621.70834531902</v>
       </c>
       <c r="K4" t="n">
+        <v>606.203075849541</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4227.91142116856</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.151754213710275</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.136309731190552</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.149328269615015</v>
       </c>
     </row>
     <row r="5">
@@ -937,7 +1132,19 @@
         <v>2909.57128555749</v>
       </c>
       <c r="K5" t="n">
+        <v>523.161965573144</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3432.73325113064</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.121914759714004</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.117637256783064</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.121242870386244</v>
       </c>
     </row>
     <row r="6">
@@ -972,7 +1179,19 @@
         <v>977.417257279866</v>
       </c>
       <c r="K6" t="n">
+        <v>411.604036177709</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1389.02129345758</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.0409550337031057</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0925525418189316</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0490597189836821</v>
       </c>
     </row>
     <row r="7">
@@ -1009,6 +1228,18 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1044,6 +1275,18 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1079,6 +1322,18 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1114,6 +1369,18 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1147,6 +1414,18 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1163,7 +1442,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1175,10 +1454,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1196,21 +1475,30 @@
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -1243,21 +1531,30 @@
         <v>774.802685321901</v>
       </c>
       <c r="L2" t="n">
+        <v>121.160390870147</v>
+      </c>
+      <c r="M2" t="n">
+        <v>895.963076192049</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.157994349106492</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
+        <v>0.167402039418822</v>
+      </c>
+      <c r="P2" t="n">
         <v>165.984590293497</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>5.49445402494167</v>
       </c>
-      <c r="O2" t="b">
+      <c r="R2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -1290,21 +1587,30 @@
         <v>1048.43084186269</v>
       </c>
       <c r="L3" t="n">
+        <v>123.897781400707</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1172.3286232634</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.213791396934109</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
+        <v>0.171184172789393</v>
+      </c>
+      <c r="P3" t="n">
         <v>128.263155586076</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>3.37150518243355</v>
       </c>
-      <c r="O3" t="b">
+      <c r="R3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -1337,21 +1643,30 @@
         <v>1082.56688047584</v>
       </c>
       <c r="L4" t="n">
+        <v>122.701921292254</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1205.2688017681</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.220752267493712</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
+        <v>0.169531904918872</v>
+      </c>
+      <c r="P4" t="n">
         <v>94.8207726180492</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>3.11053114982056</v>
       </c>
-      <c r="O4" t="b">
+      <c r="R4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -1384,21 +1699,30 @@
         <v>981.350556295445</v>
       </c>
       <c r="L5" t="n">
+        <v>123.111539109937</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1104.46209540538</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.200112680717899</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
+        <v>0.170097856031854</v>
+      </c>
+      <c r="P5" t="n">
         <v>67.5596189058994</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>3.46705241981072</v>
       </c>
-      <c r="O5" t="b">
+      <c r="R5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1431,21 +1755,30 @@
         <v>711.188353879117</v>
       </c>
       <c r="L6" t="n">
+        <v>118.001422125303</v>
+      </c>
+      <c r="M6" t="n">
+        <v>829.18977600442</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.145022394981202</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
+        <v>0.163037429775775</v>
+      </c>
+      <c r="P6" t="n">
         <v>42.2854099792372</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>4.65163472428207</v>
       </c>
-      <c r="O6" t="b">
+      <c r="R6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
@@ -1478,21 +1811,30 @@
         <v>305.650538154505</v>
       </c>
       <c r="L7" t="n">
+        <v>114.895850830196</v>
+      </c>
+      <c r="M7" t="n">
+        <v>420.546388984701</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.0623269107665869</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>0.158746597065284</v>
+      </c>
+      <c r="P7" t="n">
         <v>14.5563409421775</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>11.492216889978</v>
       </c>
-      <c r="O7" t="b">
+      <c r="R7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
@@ -1530,12 +1872,21 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8"/>
-      <c r="O8"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8"/>
+      <c r="R8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
@@ -1573,12 +1924,21 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9"/>
-      <c r="O9"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9"/>
+      <c r="R9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
@@ -1616,12 +1976,21 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10"/>
-      <c r="O10"/>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10"/>
+      <c r="R10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
@@ -1659,12 +2028,21 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11"/>
-      <c r="O11"/>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11"/>
+      <c r="R11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -1697,21 +2075,30 @@
         <v>5289.76969362412</v>
       </c>
       <c r="L12" t="n">
+        <v>709.4094652971</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5999.17915892122</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.637035867065899</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
+        <v>0.487284516477901</v>
+      </c>
+      <c r="P12" t="n">
         <v>102.592235840468</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>2.32820498414718</v>
       </c>
-      <c r="O12" t="b">
+      <c r="R12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
@@ -1744,21 +2131,30 @@
         <v>3008.33583549315</v>
       </c>
       <c r="L13" t="n">
+        <v>709.208927230334</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3717.54476272349</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.362287573634576</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
+        <v>0.487146769380238</v>
+      </c>
+      <c r="P13" t="n">
         <v>33.1220681997491</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>4.2093295531895</v>
       </c>
-      <c r="O13" t="b">
+      <c r="R13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -1791,17 +2187,26 @@
         <v>5.61796134815203</v>
       </c>
       <c r="L14" t="n">
+        <v>37.2240184416668</v>
+      </c>
+      <c r="M14" t="n">
+        <v>42.8419797898188</v>
+      </c>
+      <c r="N14" t="n">
         <v>0.000676559299524212</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14"/>
-      <c r="O14"/>
+      <c r="O14" t="n">
+        <v>0.0255687141418611</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14"/>
+      <c r="R14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -1839,12 +2244,21 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15"/>
-      <c r="O15"/>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15"/>
+      <c r="R15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
@@ -1882,12 +2296,21 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16"/>
-      <c r="O16"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16"/>
+      <c r="R16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
@@ -1925,12 +2348,21 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17"/>
-      <c r="O17"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17"/>
+      <c r="R17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
@@ -1968,12 +2400,21 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18"/>
-      <c r="O18"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18"/>
+      <c r="R18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
@@ -2011,12 +2452,21 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19"/>
-      <c r="O19"/>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19"/>
+      <c r="R19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
@@ -2054,12 +2504,21 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20"/>
-      <c r="O20"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20"/>
+      <c r="R20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n">
         <v>10</v>
@@ -2097,12 +2556,21 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21"/>
-      <c r="O21"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21"/>
+      <c r="R21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -2135,21 +2603,30 @@
         <v>3563.48587029969</v>
       </c>
       <c r="L22" t="n">
+        <v>620.005808201143</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4183.49167850084</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.334351397679096</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
+        <v>0.273415058276327</v>
+      </c>
+      <c r="P22" t="n">
         <v>143.239836673957</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>5.7233700468273</v>
       </c>
-      <c r="O22" t="b">
+      <c r="R22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
@@ -2182,21 +2659,30 @@
         <v>3869.78555030706</v>
       </c>
       <c r="L23" t="n">
+        <v>620.930595163854</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4490.71614547091</v>
+      </c>
+      <c r="N23" t="n">
         <v>0.363090595713438</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
+        <v>0.273822878135364</v>
+      </c>
+      <c r="P23" t="n">
         <v>85.4421219752872</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>4.75403411337569</v>
       </c>
-      <c r="O23" t="b">
+      <c r="R23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -2229,21 +2715,30 @@
         <v>2617.43939743668</v>
       </c>
       <c r="L24" t="n">
+        <v>622.055767182167</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3239.49516461884</v>
+      </c>
+      <c r="N24" t="n">
         <v>0.245586639803256</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
+        <v>0.274319065378917</v>
+      </c>
+      <c r="P24" t="n">
         <v>41.315672421815</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>7.09758199854391</v>
       </c>
-      <c r="O24" t="b">
+      <c r="R24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
@@ -2276,21 +2771,30 @@
         <v>607.195489618713</v>
       </c>
       <c r="L25" t="n">
+        <v>404.643753054872</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1011.83924267358</v>
+      </c>
+      <c r="N25" t="n">
         <v>0.056971366804209</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
+        <v>0.178442998209392</v>
+      </c>
+      <c r="P25" t="n">
         <v>7.63594110057332</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>31.6790958493616</v>
       </c>
-      <c r="O25" t="b">
+      <c r="R25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
@@ -2328,12 +2832,21 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26"/>
-      <c r="O26"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26"/>
+      <c r="R26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
@@ -2371,12 +2884,21 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27"/>
-      <c r="O27"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27"/>
+      <c r="R27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B28" t="n">
         <v>7</v>
@@ -2414,12 +2936,21 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28"/>
-      <c r="O28"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28"/>
+      <c r="R28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>8</v>
@@ -2457,12 +2988,21 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29"/>
-      <c r="O29"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29"/>
+      <c r="R29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
         <v>9</v>
@@ -2500,12 +3040,21 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30"/>
-      <c r="O30"/>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30"/>
+      <c r="R30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B31" t="n">
         <v>10</v>
@@ -2543,8 +3092,17 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31"/>
-      <c r="O31"/>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31"/>
+      <c r="R31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
